--- a/artfynd/A 19250-2026 artfynd.xlsx
+++ b/artfynd/A 19250-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ113"/>
+  <dimension ref="A1:AZ114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9475,48 +9475,53 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126056869</v>
+        <v>136974093</v>
       </c>
       <c r="B82" t="n">
-        <v>56876</v>
+        <v>58169</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>208257</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>667845</v>
+        <v>667852</v>
       </c>
       <c r="R82" t="n">
-        <v>6691791</v>
+        <v>6691618</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9540,12 +9545,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9565,22 +9570,22 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Shanti Wittmar</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126056869</t>
+          <t>https://artportalen.se/Sighting/136974093</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125853674</v>
+        <v>126056869</v>
       </c>
       <c r="B83" t="n">
-        <v>99035</v>
+        <v>56876</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9588,37 +9593,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219790</v>
+        <v>208257</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668118</v>
+        <v>667845</v>
       </c>
       <c r="R83" t="n">
-        <v>6691756</v>
+        <v>6691791</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9662,24 +9667,24 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren, Shanti Wittmar</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125853674</t>
+          <t>https://artportalen.se/Sighting/126056869</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125853675</v>
+        <v>125853674</v>
       </c>
       <c r="B84" t="n">
         <v>99035</v>
@@ -9714,10 +9719,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668105</v>
+        <v>668118</v>
       </c>
       <c r="R84" t="n">
-        <v>6691791</v>
+        <v>6691756</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -9775,13 +9780,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125853675</t>
+          <t>https://artportalen.se/Sighting/125853674</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125855918</v>
+        <v>125853675</v>
       </c>
       <c r="B85" t="n">
         <v>99035</v>
@@ -9812,17 +9817,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>668099</v>
+        <v>668105</v>
       </c>
       <c r="R85" t="n">
-        <v>6691912</v>
+        <v>6691791</v>
       </c>
       <c r="S85" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9866,24 +9871,24 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855918</t>
+          <t>https://artportalen.se/Sighting/125853675</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125855919</v>
+        <v>125855918</v>
       </c>
       <c r="B86" t="n">
         <v>99035</v>
@@ -9918,10 +9923,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>667939</v>
+        <v>668099</v>
       </c>
       <c r="R86" t="n">
-        <v>6691772</v>
+        <v>6691912</v>
       </c>
       <c r="S86" t="n">
         <v>12</v>
@@ -9979,13 +9984,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855919</t>
+          <t>https://artportalen.se/Sighting/125855918</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125855921</v>
+        <v>125855919</v>
       </c>
       <c r="B87" t="n">
         <v>99035</v>
@@ -10020,10 +10025,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>667940</v>
+        <v>667939</v>
       </c>
       <c r="R87" t="n">
-        <v>6691725</v>
+        <v>6691772</v>
       </c>
       <c r="S87" t="n">
         <v>12</v>
@@ -10081,13 +10086,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855921</t>
+          <t>https://artportalen.se/Sighting/125855919</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125855922</v>
+        <v>125855921</v>
       </c>
       <c r="B88" t="n">
         <v>99035</v>
@@ -10122,10 +10127,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>667907</v>
+        <v>667940</v>
       </c>
       <c r="R88" t="n">
-        <v>6691699</v>
+        <v>6691725</v>
       </c>
       <c r="S88" t="n">
         <v>12</v>
@@ -10183,13 +10188,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855922</t>
+          <t>https://artportalen.se/Sighting/125855921</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125855924</v>
+        <v>125855922</v>
       </c>
       <c r="B89" t="n">
         <v>99035</v>
@@ -10224,10 +10229,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>667949</v>
+        <v>667907</v>
       </c>
       <c r="R89" t="n">
-        <v>6691737</v>
+        <v>6691699</v>
       </c>
       <c r="S89" t="n">
         <v>12</v>
@@ -10285,13 +10290,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855924</t>
+          <t>https://artportalen.se/Sighting/125855922</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125855925</v>
+        <v>125855924</v>
       </c>
       <c r="B90" t="n">
         <v>99035</v>
@@ -10326,10 +10331,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>667944</v>
+        <v>667949</v>
       </c>
       <c r="R90" t="n">
-        <v>6691755</v>
+        <v>6691737</v>
       </c>
       <c r="S90" t="n">
         <v>12</v>
@@ -10387,13 +10392,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855925</t>
+          <t>https://artportalen.se/Sighting/125855924</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125855927</v>
+        <v>125855925</v>
       </c>
       <c r="B91" t="n">
         <v>99035</v>
@@ -10428,10 +10433,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>667941</v>
+        <v>667944</v>
       </c>
       <c r="R91" t="n">
-        <v>6691897</v>
+        <v>6691755</v>
       </c>
       <c r="S91" t="n">
         <v>12</v>
@@ -10489,13 +10494,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855927</t>
+          <t>https://artportalen.se/Sighting/125855925</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125855929</v>
+        <v>125855927</v>
       </c>
       <c r="B92" t="n">
         <v>99035</v>
@@ -10530,10 +10535,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>667863</v>
+        <v>667941</v>
       </c>
       <c r="R92" t="n">
-        <v>6691900</v>
+        <v>6691897</v>
       </c>
       <c r="S92" t="n">
         <v>12</v>
@@ -10591,13 +10596,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855929</t>
+          <t>https://artportalen.se/Sighting/125855927</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125984242</v>
+        <v>125855929</v>
       </c>
       <c r="B93" t="n">
         <v>99035</v>
@@ -10632,10 +10637,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>667892</v>
+        <v>667863</v>
       </c>
       <c r="R93" t="n">
-        <v>6691648</v>
+        <v>6691900</v>
       </c>
       <c r="S93" t="n">
         <v>12</v>
@@ -10682,24 +10687,24 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125984242</t>
+          <t>https://artportalen.se/Sighting/125855929</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126056871</v>
+        <v>125984242</v>
       </c>
       <c r="B94" t="n">
         <v>99035</v>
@@ -10734,13 +10739,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>668083</v>
+        <v>667892</v>
       </c>
       <c r="R94" t="n">
-        <v>6691848</v>
+        <v>6691648</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10784,71 +10789,62 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Shanti Wittmar</t>
+          <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126056871</t>
+          <t>https://artportalen.se/Sighting/125984242</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125807878</v>
+        <v>126056871</v>
       </c>
       <c r="B95" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>668030</v>
+        <v>668083</v>
       </c>
       <c r="R95" t="n">
-        <v>6691905</v>
+        <v>6691848</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10883,11 +10879,6 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Vid stenblock</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -10905,19 +10896,19 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Ingemar Södergren, Shanti Wittmar</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807878</t>
+          <t>https://artportalen.se/Sighting/126056871</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127382951</v>
+        <v>125807878</v>
       </c>
       <c r="B96" t="n">
         <v>99118</v>
@@ -10945,17 +10936,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>667939</v>
+        <v>668030</v>
       </c>
       <c r="R96" t="n">
-        <v>6691920</v>
+        <v>6691905</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10982,17 +10982,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>1 m väster om stor gran</t>
+          <t>Vid stenblock</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11018,60 +11018,51 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382951</t>
+          <t>https://artportalen.se/Sighting/125807878</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125807883</v>
+        <v>127382951</v>
       </c>
       <c r="B97" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668026</v>
+        <v>667939</v>
       </c>
       <c r="R97" t="n">
-        <v>6691901</v>
+        <v>6691920</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -11098,12 +11089,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>1 m väster om stor gran</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11129,13 +11125,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807883</t>
+          <t>https://artportalen.se/Sighting/127382951</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125832167</v>
+        <v>125807883</v>
       </c>
       <c r="B98" t="n">
         <v>106244</v>
@@ -11163,17 +11159,26 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>667940</v>
+        <v>668026</v>
       </c>
       <c r="R98" t="n">
-        <v>6691828</v>
+        <v>6691901</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -11220,24 +11225,24 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125832167</t>
+          <t>https://artportalen.se/Sighting/125807883</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125855909</v>
+        <v>125832167</v>
       </c>
       <c r="B99" t="n">
         <v>106244</v>
@@ -11272,13 +11277,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>667931</v>
+        <v>667940</v>
       </c>
       <c r="R99" t="n">
-        <v>6691727</v>
+        <v>6691828</v>
       </c>
       <c r="S99" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11322,24 +11327,24 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855909</t>
+          <t>https://artportalen.se/Sighting/125832167</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127382952</v>
+        <v>125855909</v>
       </c>
       <c r="B100" t="n">
         <v>106244</v>
@@ -11370,17 +11375,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>667937</v>
+        <v>667931</v>
       </c>
       <c r="R100" t="n">
-        <v>6691815</v>
+        <v>6691727</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11404,12 +11409,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11424,24 +11429,24 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382952</t>
+          <t>https://artportalen.se/Sighting/125855909</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127382953</v>
+        <v>127382952</v>
       </c>
       <c r="B101" t="n">
         <v>106244</v>
@@ -11476,10 +11481,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>667945</v>
+        <v>667937</v>
       </c>
       <c r="R101" t="n">
-        <v>6691904</v>
+        <v>6691815</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11537,13 +11542,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382953</t>
+          <t>https://artportalen.se/Sighting/127382952</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127382954</v>
+        <v>127382953</v>
       </c>
       <c r="B102" t="n">
         <v>106244</v>
@@ -11578,10 +11583,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>667953</v>
+        <v>667945</v>
       </c>
       <c r="R102" t="n">
-        <v>6691911</v>
+        <v>6691904</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11639,13 +11644,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382954</t>
+          <t>https://artportalen.se/Sighting/127382953</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127382955</v>
+        <v>127382954</v>
       </c>
       <c r="B103" t="n">
         <v>106244</v>
@@ -11673,26 +11678,17 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>667920</v>
+        <v>667953</v>
       </c>
       <c r="R103" t="n">
-        <v>6691884</v>
+        <v>6691911</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11750,16 +11746,16 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382955</t>
+          <t>https://artportalen.se/Sighting/127382954</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125855900</v>
+        <v>127382955</v>
       </c>
       <c r="B104" t="n">
-        <v>97983</v>
+        <v>106244</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11767,37 +11763,46 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>668113</v>
+        <v>667920</v>
       </c>
       <c r="R104" t="n">
-        <v>6691886</v>
+        <v>6691884</v>
       </c>
       <c r="S104" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11821,12 +11826,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11841,24 +11846,24 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855900</t>
+          <t>https://artportalen.se/Sighting/127382955</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125855902</v>
+        <v>125855900</v>
       </c>
       <c r="B105" t="n">
         <v>97983</v>
@@ -11893,10 +11898,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>667921</v>
+        <v>668113</v>
       </c>
       <c r="R105" t="n">
-        <v>6691714</v>
+        <v>6691886</v>
       </c>
       <c r="S105" t="n">
         <v>12</v>
@@ -11954,13 +11959,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855902</t>
+          <t>https://artportalen.se/Sighting/125855900</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125855903</v>
+        <v>125855902</v>
       </c>
       <c r="B106" t="n">
         <v>97983</v>
@@ -11995,10 +12000,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>667902</v>
+        <v>667921</v>
       </c>
       <c r="R106" t="n">
-        <v>6691700</v>
+        <v>6691714</v>
       </c>
       <c r="S106" t="n">
         <v>12</v>
@@ -12056,13 +12061,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855903</t>
+          <t>https://artportalen.se/Sighting/125855902</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125855905</v>
+        <v>125855903</v>
       </c>
       <c r="B107" t="n">
         <v>97983</v>
@@ -12097,10 +12102,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>667920</v>
+        <v>667902</v>
       </c>
       <c r="R107" t="n">
-        <v>6691730</v>
+        <v>6691700</v>
       </c>
       <c r="S107" t="n">
         <v>12</v>
@@ -12158,16 +12163,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855905</t>
+          <t>https://artportalen.se/Sighting/125855903</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125807906</v>
+        <v>125855905</v>
       </c>
       <c r="B108" t="n">
-        <v>101326</v>
+        <v>97983</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12175,21 +12180,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12199,13 +12204,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>667888</v>
+        <v>667920</v>
       </c>
       <c r="R108" t="n">
-        <v>6691884</v>
+        <v>6691730</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12249,24 +12254,24 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807906</t>
+          <t>https://artportalen.se/Sighting/125855905</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125807907</v>
+        <v>125807906</v>
       </c>
       <c r="B109" t="n">
         <v>101326</v>
@@ -12301,10 +12306,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>667915</v>
+        <v>667888</v>
       </c>
       <c r="R109" t="n">
-        <v>6691893</v>
+        <v>6691884</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -12362,13 +12367,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807907</t>
+          <t>https://artportalen.se/Sighting/125807906</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125832173</v>
+        <v>125807907</v>
       </c>
       <c r="B110" t="n">
         <v>101326</v>
@@ -12403,10 +12408,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>668118</v>
+        <v>667915</v>
       </c>
       <c r="R110" t="n">
-        <v>6691903</v>
+        <v>6691893</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -12453,24 +12458,24 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125832173</t>
+          <t>https://artportalen.se/Sighting/125807907</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125855930</v>
+        <v>125832173</v>
       </c>
       <c r="B111" t="n">
         <v>101326</v>
@@ -12505,13 +12510,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>667952</v>
+        <v>668118</v>
       </c>
       <c r="R111" t="n">
-        <v>6691797</v>
+        <v>6691903</v>
       </c>
       <c r="S111" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12555,24 +12560,24 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855930</t>
+          <t>https://artportalen.se/Sighting/125832173</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125855931</v>
+        <v>125855930</v>
       </c>
       <c r="B112" t="n">
         <v>101326</v>
@@ -12607,10 +12612,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>667892</v>
+        <v>667952</v>
       </c>
       <c r="R112" t="n">
-        <v>6691878</v>
+        <v>6691797</v>
       </c>
       <c r="S112" t="n">
         <v>12</v>
@@ -12668,13 +12673,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855931</t>
+          <t>https://artportalen.se/Sighting/125855930</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127382966</v>
+        <v>125855931</v>
       </c>
       <c r="B113" t="n">
         <v>101326</v>
@@ -12705,17 +12710,17 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>668001</v>
+        <v>667892</v>
       </c>
       <c r="R113" t="n">
-        <v>6691848</v>
+        <v>6691878</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12739,12 +12744,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12759,16 +12764,118 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855931</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>127382966</v>
+      </c>
+      <c r="B114" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>668001</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6691848</v>
+      </c>
+      <c r="S114" t="n">
+        <v>15</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127382966</t>
         </is>
@@ -12888,6 +12995,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19250-2026 artfynd.xlsx
+++ b/artfynd/A 19250-2026 artfynd.xlsx
@@ -9478,7 +9478,7 @@
         <v>136974093</v>
       </c>
       <c r="B82" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 19250-2026 artfynd.xlsx
+++ b/artfynd/A 19250-2026 artfynd.xlsx
@@ -9478,7 +9478,7 @@
         <v>136974093</v>
       </c>
       <c r="B82" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9504,11 +9504,7 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>

--- a/artfynd/A 19250-2026 artfynd.xlsx
+++ b/artfynd/A 19250-2026 artfynd.xlsx
@@ -9478,7 +9478,7 @@
         <v>136974093</v>
       </c>
       <c r="B82" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 19250-2026 artfynd.xlsx
+++ b/artfynd/A 19250-2026 artfynd.xlsx
@@ -9478,7 +9478,7 @@
         <v>136974093</v>
       </c>
       <c r="B82" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 19250-2026 artfynd.xlsx
+++ b/artfynd/A 19250-2026 artfynd.xlsx
@@ -9478,7 +9478,7 @@
         <v>136974093</v>
       </c>
       <c r="B82" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 19250-2026 artfynd.xlsx
+++ b/artfynd/A 19250-2026 artfynd.xlsx
@@ -9478,7 +9478,7 @@
         <v>136974093</v>
       </c>
       <c r="B82" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
